--- a/originales/respuestas/2025/01. Calificadas/bucle p14/Secretaría Distrital De Hábitat.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p14/Secretaría Distrital De Hábitat.xlsx
@@ -488,9 +488,9 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="2" width="10.71"/>
-    <col customWidth="1" min="3" max="3" width="54.57"/>
+    <col customWidth="1" min="3" max="3" width="76.57"/>
     <col customWidth="1" min="4" max="5" width="10.71"/>
-    <col customWidth="1" min="6" max="6" width="52.0"/>
+    <col customWidth="1" min="6" max="6" width="83.57"/>
     <col customWidth="1" min="7" max="26" width="10.71"/>
   </cols>
   <sheetData>
